--- a/data/input/pureComponents_2026DecJANNAF_training_actual.xlsx
+++ b/data/input/pureComponents_2026DecJANNAF_training_actual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310B27CD-B914-4C48-AD6C-0C94E5B6015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734285A3-995C-46CE-ACE5-6C049EBD6D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{22E7D031-F429-4E0A-8A8B-4D129F5BB641}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{22E7D031-F429-4E0A-8A8B-4D129F5BB641}"/>
   </bookViews>
   <sheets>
     <sheet name="Unfinished CATALOG" sheetId="1" r:id="rId1"/>
@@ -885,7 +885,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="152">
   <si>
     <t>Full Name</t>
   </si>
@@ -1341,6 +1341,9 @@
   </si>
   <si>
     <t>CCCCCCCCCCN.[B]</t>
+  </si>
+  <si>
+    <t>CC[N+](CC)(CC)CC.[Br-]</t>
   </si>
 </sst>
 </file>
@@ -2306,7 +2309,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE786A1-84C7-4241-A3B9-138356725320}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -2467,34 +2470,34 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="D5">
-        <v>531.08999999999992</v>
+        <v>540</v>
       </c>
       <c r="E5">
-        <v>6.0952604538280424</v>
+        <v>131.52186130069785</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5">
-        <v>51.24</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>4.5254833995939059</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
-        <v>-396.29999999999995</v>
+        <v>-363.45</v>
       </c>
       <c r="K5">
-        <v>18.966988866624746</v>
+        <v>15.700212312789498</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -2502,34 +2505,34 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" t="s">
-        <v>141</v>
+        <v>97</v>
+      </c>
+      <c r="D6">
+        <v>531.08999999999992</v>
+      </c>
+      <c r="E6">
+        <v>6.0952604538280424</v>
       </c>
       <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>51.24</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
-      <c r="G6" t="s">
-        <v>141</v>
-      </c>
-      <c r="H6" t="s">
-        <v>141</v>
-      </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>-316.17500000000001</v>
+        <v>-396.29999999999995</v>
       </c>
       <c r="K6">
-        <v>12.790198069876276</v>
+        <v>18.966988866624746</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -2537,19 +2540,19 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7">
-        <v>264.14999999999998</v>
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>141</v>
       </c>
       <c r="E7" t="s">
         <v>141</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
         <v>141</v>
@@ -2560,40 +2563,40 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" t="s">
-        <v>141</v>
-      </c>
-      <c r="K7" t="s">
-        <v>141</v>
+      <c r="J7">
+        <v>-316.17500000000001</v>
+      </c>
+      <c r="K7">
+        <v>12.790198069876276</v>
       </c>
       <c r="L7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8">
+        <v>264.14999999999998</v>
+      </c>
+      <c r="E8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I8">
         <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8">
-        <v>373.875</v>
-      </c>
-      <c r="E8">
-        <v>4.6315494167718541</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>13.749600000000001</v>
-      </c>
-      <c r="H8">
-        <v>3.0399934736772081</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
       </c>
       <c r="J8" t="s">
         <v>141</v>
@@ -2607,69 +2610,69 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9">
+        <v>373.875</v>
+      </c>
+      <c r="E9">
+        <v>4.6315494167718541</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>13.749600000000001</v>
+      </c>
+      <c r="H9">
+        <v>3.0399934736772081</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>141</v>
+      </c>
+      <c r="K9" t="s">
+        <v>141</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>123</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>124</v>
       </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" t="s">
-        <v>141</v>
-      </c>
-      <c r="F9">
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F10">
         <v>0</v>
       </c>
-      <c r="G9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H9" t="s">
-        <v>141</v>
-      </c>
-      <c r="I9">
+      <c r="G10" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" t="s">
+        <v>141</v>
+      </c>
+      <c r="I10">
         <v>0</v>
       </c>
-      <c r="J9">
+      <c r="J10">
         <v>-256.83333333333331</v>
       </c>
-      <c r="K9">
+      <c r="K10">
         <v>9.6738479072876338</v>
-      </c>
-      <c r="L9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10">
-        <v>639.63</v>
-      </c>
-      <c r="E10">
-        <v>46.349679610543141</v>
-      </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10">
-        <v>20.49</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10">
-        <v>-274.8</v>
-      </c>
-      <c r="K10">
-        <v>2.4331050121192805</v>
       </c>
       <c r="L10">
         <v>3</v>
@@ -2677,34 +2680,34 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E11" t="s">
-        <v>141</v>
+        <v>95</v>
+      </c>
+      <c r="D11">
+        <v>639.63</v>
+      </c>
+      <c r="E11">
+        <v>46.349679610543141</v>
       </c>
       <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>20.49</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
-      <c r="G11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H11" t="s">
-        <v>141</v>
-      </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>-199.13333333333333</v>
+        <v>-274.8</v>
       </c>
       <c r="K11">
-        <v>7.9122268251948746</v>
+        <v>2.4331050121192805</v>
       </c>
       <c r="L11">
         <v>3</v>
@@ -2712,63 +2715,63 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12">
-        <v>376.02499999999998</v>
-      </c>
-      <c r="E12">
-        <v>0.17677669529663689</v>
+        <v>126</v>
+      </c>
+      <c r="D12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" t="s">
+        <v>141</v>
       </c>
       <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>40.760800000000003</v>
-      </c>
-      <c r="H12">
-        <v>0.93451232201614376</v>
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>141</v>
+      </c>
+      <c r="H12" t="s">
+        <v>141</v>
       </c>
       <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="J12" t="s">
-        <v>141</v>
-      </c>
-      <c r="K12" t="s">
-        <v>141</v>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>-199.13333333333333</v>
+      </c>
+      <c r="K12">
+        <v>7.9122268251948746</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D13">
-        <v>295.14999999999998</v>
-      </c>
-      <c r="E13" t="s">
-        <v>141</v>
+        <v>376.02499999999998</v>
+      </c>
+      <c r="E13">
+        <v>0.17677669529663689</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>1.29704</v>
-      </c>
-      <c r="H13" t="s">
-        <v>141</v>
+        <v>40.760800000000003</v>
+      </c>
+      <c r="H13">
+        <v>0.93451232201614376</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="s">
         <v>141</v>
@@ -2782,13 +2785,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D14">
-        <v>412.15</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="E14" t="s">
         <v>141</v>
@@ -2797,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>39.329600000000006</v>
+        <v>1.29704</v>
       </c>
       <c r="H14" t="s">
         <v>141</v>
@@ -2817,13 +2820,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="D15">
-        <v>583</v>
+        <v>412.15</v>
       </c>
       <c r="E15" t="s">
         <v>141</v>
@@ -2832,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>7.3</v>
+        <v>39.329600000000006</v>
       </c>
       <c r="H15" t="s">
         <v>141</v>
@@ -2840,113 +2843,113 @@
       <c r="I15">
         <v>1</v>
       </c>
-      <c r="J15">
-        <v>-442</v>
+      <c r="J15" t="s">
+        <v>141</v>
       </c>
       <c r="K15" t="s">
         <v>141</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D16">
-        <v>473.87333333333328</v>
-      </c>
-      <c r="E16">
-        <v>49.990995522527193</v>
+        <v>583</v>
+      </c>
+      <c r="E16" t="s">
+        <v>141</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>66.58</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
+        <v>7.3</v>
+      </c>
+      <c r="H16" t="s">
+        <v>141</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>-487.5</v>
-      </c>
-      <c r="K16">
-        <v>17.677669529663689</v>
+        <v>-442</v>
+      </c>
+      <c r="K16" t="s">
+        <v>141</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" t="s">
-        <v>141</v>
+        <v>98</v>
+      </c>
+      <c r="D17">
+        <v>473.87333333333328</v>
+      </c>
+      <c r="E17">
+        <v>49.990995522527193</v>
       </c>
       <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>66.58</v>
+      </c>
+      <c r="H17">
         <v>0</v>
       </c>
-      <c r="G17" t="s">
-        <v>141</v>
-      </c>
-      <c r="H17" t="s">
-        <v>141</v>
-      </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>-395</v>
-      </c>
-      <c r="K17" t="s">
-        <v>141</v>
+        <v>-487.5</v>
+      </c>
+      <c r="K17">
+        <v>17.677669529663689</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18">
-        <v>673.15</v>
+        <v>134</v>
+      </c>
+      <c r="D18" t="s">
+        <v>141</v>
       </c>
       <c r="E18" t="s">
         <v>141</v>
       </c>
       <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>141</v>
       </c>
       <c r="H18" t="s">
         <v>141</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>-191.84</v>
+        <v>-395</v>
       </c>
       <c r="K18" t="s">
         <v>141</v>
@@ -2957,13 +2960,13 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="D19">
-        <v>878.15</v>
+        <v>673.15</v>
       </c>
       <c r="E19" t="s">
         <v>141</v>
@@ -2972,7 +2975,7 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
         <v>141</v>
@@ -2981,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>-226.9</v>
+        <v>-191.84</v>
       </c>
       <c r="K19" t="s">
         <v>141</v>
@@ -2992,13 +2995,13 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D20">
-        <v>559.15</v>
+        <v>878.15</v>
       </c>
       <c r="E20" t="s">
         <v>141</v>
@@ -3007,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>7.14</v>
+        <v>19.2</v>
       </c>
       <c r="H20" t="s">
         <v>141</v>
@@ -3016,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>-190.46</v>
+        <v>-226.9</v>
       </c>
       <c r="K20" t="s">
         <v>141</v>
@@ -3027,22 +3030,22 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="D21">
-        <v>881.15</v>
-      </c>
-      <c r="E21">
-        <v>6.2449979983983983</v>
+        <v>559.15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>141</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>19.899999999999999</v>
+        <v>7.14</v>
       </c>
       <c r="H21" t="s">
         <v>141</v>
@@ -3051,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>-408.6</v>
+        <v>-190.46</v>
       </c>
       <c r="K21" t="s">
         <v>141</v>
@@ -3062,22 +3065,22 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22">
-        <v>1045.1500000000001</v>
+        <v>881.15</v>
       </c>
       <c r="E22">
-        <v>1.4142135623730951</v>
+        <v>6.2449979983983983</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>26.317360000000001</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="H22" t="s">
         <v>141</v>
@@ -3086,7 +3089,7 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>-436.68</v>
+        <v>-408.6</v>
       </c>
       <c r="K22" t="s">
         <v>141</v>
@@ -3096,23 +3099,23 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>111</v>
+      <c r="A23" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D23">
-        <v>1074.075</v>
+        <v>1045.1500000000001</v>
       </c>
       <c r="E23">
-        <v>8.6602540378496379E-2</v>
+        <v>1.4142135623730951</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>30.388680025600006</v>
+        <v>26.317360000000001</v>
       </c>
       <c r="H23" t="s">
         <v>141</v>
@@ -3121,33 +3124,33 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>-411.01</v>
-      </c>
-      <c r="K23">
-        <v>0.15556349186105975</v>
+        <v>-436.68</v>
+      </c>
+      <c r="K23" t="s">
+        <v>141</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="D24">
-        <v>243.24999999999997</v>
-      </c>
-      <c r="E24" t="s">
-        <v>141</v>
+        <v>1074.075</v>
+      </c>
+      <c r="E24">
+        <v>8.6602540378496379E-2</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>10.9</v>
+        <v>30.388680025600006</v>
       </c>
       <c r="H24" t="s">
         <v>141</v>
@@ -3155,25 +3158,25 @@
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K24" t="s">
-        <v>141</v>
+      <c r="J24">
+        <v>-411.01</v>
+      </c>
+      <c r="K24">
+        <v>0.15556349186105975</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="D25">
-        <v>281.64999999999998</v>
+        <v>243.24999999999997</v>
       </c>
       <c r="E25" t="s">
         <v>141</v>
@@ -3182,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>15.4</v>
+        <v>10.9</v>
       </c>
       <c r="H25" t="s">
         <v>141</v>
@@ -3202,13 +3205,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D26">
-        <v>307.84999999999997</v>
+        <v>281.64999999999998</v>
       </c>
       <c r="E26" t="s">
         <v>141</v>
@@ -3217,7 +3220,7 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>23.6</v>
+        <v>15.4</v>
       </c>
       <c r="H26" t="s">
         <v>141</v>
@@ -3237,13 +3240,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D27">
-        <v>323.04999999999995</v>
+        <v>307.84999999999997</v>
       </c>
       <c r="E27" t="s">
         <v>141</v>
@@ -3252,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="G27">
-        <v>30.7</v>
+        <v>23.6</v>
       </c>
       <c r="H27" t="s">
         <v>141</v>
@@ -3272,13 +3275,13 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D28">
-        <v>366.65</v>
+        <v>323.04999999999995</v>
       </c>
       <c r="E28" t="s">
         <v>141</v>
@@ -3286,14 +3289,14 @@
       <c r="F28">
         <v>1</v>
       </c>
-      <c r="G28" t="s">
-        <v>141</v>
+      <c r="G28">
+        <v>30.7</v>
       </c>
       <c r="H28" t="s">
         <v>141</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="s">
         <v>141</v>
@@ -3307,13 +3310,13 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D29">
-        <v>310.14999999999998</v>
+        <v>366.65</v>
       </c>
       <c r="E29" t="s">
         <v>141</v>
@@ -3342,71 +3345,106 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="D30">
-        <v>179.32</v>
-      </c>
-      <c r="E30">
-        <v>1.3349157276772183</v>
+        <v>310.14999999999998</v>
+      </c>
+      <c r="E30" t="s">
+        <v>141</v>
       </c>
       <c r="F30">
-        <v>5</v>
-      </c>
-      <c r="G30">
-        <v>5.9405000000000001</v>
-      </c>
-      <c r="H30">
-        <v>7.0710678118615568E-4</v>
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>141</v>
+      </c>
+      <c r="H30" t="s">
+        <v>141</v>
       </c>
       <c r="I30">
-        <v>2</v>
-      </c>
-      <c r="J30">
-        <v>-21.4</v>
-      </c>
-      <c r="K30">
-        <v>3.3941125496954587</v>
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>141</v>
+      </c>
+      <c r="K30" t="s">
+        <v>141</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D31">
-        <v>153.26</v>
+        <v>179.32</v>
       </c>
       <c r="E31">
-        <v>3.6390932936653244</v>
+        <v>1.3349157276772183</v>
       </c>
       <c r="F31">
         <v>5</v>
       </c>
       <c r="G31">
-        <v>6.5419999999999998</v>
+        <v>5.9405000000000001</v>
       </c>
       <c r="H31">
-        <v>2.8284271247458787E-3</v>
+        <v>7.0710678118615568E-4</v>
       </c>
       <c r="I31">
         <v>2</v>
       </c>
       <c r="J31">
+        <v>-21.4</v>
+      </c>
+      <c r="K31">
+        <v>3.3941125496954587</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32">
+        <v>153.26</v>
+      </c>
+      <c r="E32">
+        <v>3.6390932936653244</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>6.5419999999999998</v>
+      </c>
+      <c r="H32">
+        <v>2.8284271247458787E-3</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
         <v>-27.2</v>
       </c>
-      <c r="K31">
+      <c r="K32">
         <v>4.9497474683058327</v>
       </c>
-      <c r="L31">
+      <c r="L32">
         <v>2</v>
       </c>
     </row>
